--- a/results/log_pv_cap_per_inst/log_pv_cap_per_inst_densities_fdensity_effects.xlsx
+++ b/results/log_pv_cap_per_inst/log_pv_cap_per_inst_densities_fdensity_effects.xlsx
@@ -511,388 +511,388 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>fdensity</t>
+          <t>D(Firms)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>-0.408</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>-0.006</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-0.402</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>-0.074</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>-0.007</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>-0.000</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-0.067</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-0.037</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-0.010</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-0.027</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>-0.053</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-0.006</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>-0.046</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>-0.013</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>-0.007</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>-0.001</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>-0.000</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>-0.001</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>-0.001</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-0.000</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-0.000</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>-0.001</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-0.000</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>-0.000</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>-0.000</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>-0.000</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-0.000</t>
+          <t>-0.006</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-0.000</t>
+          <t>-0.014</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>-0.000</t>
+          <t>-0.009</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-0.000</t>
+          <t>-0.005</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>log_income</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>4.276</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.004</t>
+          <t>-0.118</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>4.393</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.016</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>1.838</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>1.570</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>0.241</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>1.329</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>1.376</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.163</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>1.212</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>1.273</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.650</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0.624</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>1.291</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0.010</t>
+          <t>0.830</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.461</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>log_hholds</t>
+          <t>Households</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>3.038</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.000</t>
+          <t>0.003</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>3.035</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.182</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.006</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.176</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.230</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.001</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.229</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.035</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.004</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.030</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.017</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.009</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.008</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.006</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.004</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.002</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>log_sunny_hours</t>
+          <t>Sunny hours</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-0.002</t>
+          <t>-0.109</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.004</t>
+          <t>-0.165</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.055</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.020</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.004</t>
+          <t>-0.158</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.177</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.067</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.004</t>
+          <t>-0.170</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0.237</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>-0.518</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.002</t>
+          <t>-0.061</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-0.009</t>
+          <t>-0.456</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>-0.002</t>
+          <t>-0.098</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-0.001</t>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-0.001</t>
+          <t>-0.048</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-0.002</t>
+          <t>-0.065</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>-0.001</t>
+          <t>-0.042</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-0.000</t>
+          <t>-0.023</t>
         </is>
       </c>
     </row>
